--- a/artfynd/A 42548-2021 artfynd.xlsx
+++ b/artfynd/A 42548-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42548-2021 artfynd.xlsx
+++ b/artfynd/A 42548-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111873132</v>
+        <v>111872844</v>
       </c>
       <c r="B2" t="n">
-        <v>90844</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pikku Myllynoja (Pikku Myllynoja), Lu lm</t>
+          <t>Pikku Myllynoja, Pikku Myllynoja, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>789572</v>
+        <v>789476</v>
       </c>
       <c r="R2" t="n">
-        <v>7434799</v>
+        <v>7434822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111873080</v>
+        <v>111872933</v>
       </c>
       <c r="B3" t="n">
-        <v>90792</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pikku Myllynoja (Pikku Myllynoja), Lu lm</t>
+          <t>Pikku Myllynoja, Pikku Myllynoja, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789572</v>
+        <v>789476</v>
       </c>
       <c r="R3" t="n">
-        <v>7434799</v>
+        <v>7434822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +868,201 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111873080</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pikku Myllynoja, Pikku Myllynoja, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>789572</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7434799</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128289155</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pikku Myllynoja, Pikku Myllynoja, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>789505</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7434850</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
